--- a/out/Attention-Mamba1_repeat_3_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.637571854792519</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001122823411441641</v>
+        <v>-0.0001676808107870165</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1289908441631052</v>
+        <v>-0.1926330455260462</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.637571854792519</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.637571854792519</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.637571854792519</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.138476860958186</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.138476860958186</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1928007263368332</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1292152265751893</v>
+        <v>-0.192941863446285</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4030863253614042</v>
+        <v>0.507496902937696</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.637571854792519</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6777313646528288</v>
+        <v>0.8230263550666476</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02871977946537345</v>
+        <v>0.03615901119606519</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3314380768476958</v>
+        <v>0.3870334671199133</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05036470774703015</v>
+        <v>0.06341071381903395</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4034383121615276</v>
+        <v>0.4776837432632751</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06118748367439239</v>
+        <v>0.07703621675771917</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4754435228708289</v>
+        <v>0.568340053545339</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01619174124472059</v>
+        <v>0.02038571311170338</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4465614014700952</v>
+        <v>0.5319766141714982</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008994751033330171</v>
+        <v>0.01132585934794351</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4483443344801525</v>
+        <v>0.5342226929083159</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01889922796852329</v>
+        <v>0.02379623135082797</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4771605839490041</v>
+        <v>0.5705040773620281</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007422514537920812</v>
+        <v>0.009345699453332234</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4730887949690633</v>
+        <v>0.5653789557053144</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005283651124441467</v>
+        <v>0.006654974556904275</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4762322139297354</v>
+        <v>0.569338097650578</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002076647207830297</v>
+        <v>0.002615730013771998</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4750973736886652</v>
+        <v>0.5679107585939877</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001177263899096263</v>
+        <v>0.001482463706164138</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4753726826044586</v>
+        <v>0.5682586126151178</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004447834153510995</v>
+        <v>0.0005622203384192717</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4750852155717455</v>
+        <v>0.5678978578329117</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002063844051359051</v>
+        <v>0.0002603314668632975</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.475051705822261</v>
+        <v>0.567856998660794</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.250322825798153e-05</v>
+        <v>9.268636061683091e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4749901505523489</v>
+        <v>0.5677807154560089</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.789531607963211e-05</v>
+        <v>2.361914509954013e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4749533641125958</v>
+        <v>0.5677356516698914</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>9.309572549770066e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4749483462411868</v>
+        <v>0.5677306293306302</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>2.705352179376644e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4749442187401079</v>
+        <v>0.5677267567027733</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>5.776969076452056e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4749414175942303</v>
+        <v>0.5677246885082696</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-2.504786695239595e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4749359738492239</v>
+        <v>0.5677190968482613</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4749299811157936</v>
+        <v>0.5677127728542534</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4749246133272152</v>
+        <v>0.5677074050656751</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4749246500757069</v>
+        <v>0.5677074418141668</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4749247603211824</v>
+        <v>0.5677075520596423</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.474924833818166</v>
+        <v>0.5677076255566259</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.434846904977811</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4749250175606252</v>
+        <v>0.567707809299085</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4749265609972817</v>
+        <v>0.5677093527357415</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.138476860958186</v>
+        <v>2.367222099549092</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4749280309369548</v>
+        <v>0.5677108226754146</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4749292803856768</v>
+        <v>0.5677120721241367</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.138476860958186</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4749306400798741</v>
+        <v>0.5677134318183339</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5384768609581863</v>
+        <v>2.967222099549092</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4749284351703648</v>
+        <v>0.5677112269088246</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4749280309369548</v>
+        <v>0.5677108226754146</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4749271857216428</v>
+        <v>0.5677099774601027</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4749277369490201</v>
+        <v>0.56771052868748</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4749274062125937</v>
+        <v>0.5677101979510535</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4749271122246592</v>
+        <v>0.567709903963119</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4749271857216428</v>
+        <v>0.5677099774601027</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4749267447397408</v>
+        <v>0.5677095364782007</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4749266344942653</v>
+        <v>0.5677094262327251</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4749265977457736</v>
+        <v>0.5677093894842334</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4749267447397408</v>
+        <v>0.5677095364782007</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4749262670093472</v>
+        <v>0.5677090587478071</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4749272224701345</v>
+        <v>0.5677100142085943</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4749271857216428</v>
+        <v>0.5677099774601027</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4749268549852164</v>
+        <v>0.5677096467236762</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4749272959671184</v>
+        <v>0.5677100877055782</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4749266712427572</v>
+        <v>0.5677094629812171</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4749264875002981</v>
+        <v>0.5677092792387579</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4749260832668881</v>
+        <v>0.5677088750053478</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.474925238051576</v>
+        <v>0.5677080297900359</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4749252013030844</v>
+        <v>0.5677079930415442</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4749253482970516</v>
+        <v>0.5677081400355115</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.474925274800068</v>
+        <v>0.5677080665385278</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4749253482970516</v>
+        <v>0.5677081400355115</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4749253850455435</v>
+        <v>0.5677081767840034</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.474925274800068</v>
+        <v>0.5677080665385278</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.47492571578197</v>
+        <v>0.5677085075204298</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4749256055364944</v>
+        <v>0.5677083972749543</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4749255687880025</v>
+        <v>0.5677083605264623</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4749254952910189</v>
+        <v>0.5677082870294787</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4749254585425272</v>
+        <v>0.567708250280987</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.474925238051576</v>
+        <v>0.5677080297900359</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5384768609581863</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4749251645545924</v>
+        <v>0.5677079562930523</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4749250910576088</v>
+        <v>0.5677078827960687</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4749251278061007</v>
+        <v>0.5677079195445606</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4749250175606252</v>
+        <v>0.567707809299085</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4749251278061007</v>
+        <v>0.5677079195445606</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.138476860958186</v>
+        <v>-1.034846904977811</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4749254217940352</v>
+        <v>0.5677082135324951</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.5539754264574855</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.138476860958186</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432806</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-2.637571854792519</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.138476860958186</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-2.637571854792519</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.138476860958186</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001122823411441641</v>
+        <v>-9.564317593548912e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1289908441631052</v>
+        <v>-0.1098756391847005</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1291031265042494</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.138476860958186</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1292152265751893</v>
+        <v>-0.1099712823606361</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4030863253614042</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6777313646528288</v>
+        <v>-0.110056073578537</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02871977946537345</v>
+        <v>-0.1138592459437131</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3314380768476958</v>
+        <v>-0.2239153195222502</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05036470774703015</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4034383121615276</v>
+        <v>-0.2239892018635536</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06118748367439239</v>
+        <v>0.06765632548313105</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4754435228708289</v>
+        <v>-0.0884635567722664</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01619174124472059</v>
+        <v>0.006721339656880313</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432806</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4465614014700952</v>
+        <v>-0.1428246047627267</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008994751033330171</v>
+        <v>0.005054802979138153</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4483443344801525</v>
+        <v>-0.1394664796510547</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01889922796852329</v>
+        <v>0.0296347560280399</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4771605839490041</v>
+        <v>-0.0852288288384925</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007422514537920812</v>
+        <v>0.01100510795767507</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4730887949690633</v>
+        <v>-0.09288798588976532</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005283651124441467</v>
+        <v>0.008465071840913154</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4762322139297354</v>
+        <v>-0.08696730612569047</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002076647207830297</v>
+        <v>0.003171480968060904</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.138476860958186</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4750973736886652</v>
+        <v>-0.08909863252768305</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001177263899096263</v>
+        <v>0.001848062684090923</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.7169524225432804</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4753726826044586</v>
+        <v>-0.08857627168610552</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004447834153510995</v>
+        <v>0.0006562505770910311</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4750852155717455</v>
+        <v>-0.08911269341112871</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002063844051359051</v>
+        <v>0.0002995832812366127</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.475051705822261</v>
+        <v>-0.08917129767969041</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.250322825798153e-05</v>
+        <v>9.401545328678301e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4749901505523489</v>
+        <v>-0.08928263279871038</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.789531607963211e-05</v>
+        <v>1.477716780084401e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4749533641125958</v>
+        <v>-0.08934756310967355</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>4.888583900422008e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432806</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4749483462411868</v>
+        <v>-0.08935259661856526</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>8.983661582139364e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4749442187401079</v>
+        <v>-0.08935592432896665</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-1.603006223559316e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.7169524225432804</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4749414175942303</v>
+        <v>-0.08935670935394999</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-2.800616699423805e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.037571854792519</v>
+        <v>-1.44290641471487</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4749359738492239</v>
+        <v>-0.08936259684396244</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.7169524225432805</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4749299811157936</v>
+        <v>-0.0894373131227597</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>-0.06131849295370218</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.138476860958186</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4749246133272152</v>
+        <v>-0.1507560265674128</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4749246500757069</v>
+        <v>-0.1508586901870591</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0</v>
+        <v>0.03884276342406302</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4749247603211824</v>
+        <v>-0.07296047486886394</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0</v>
+        <v>0.03242030125742617</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.474924833818166</v>
+        <v>-0.04704932372256357</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0</v>
+        <v>0.0324589833099528</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4749250175606252</v>
+        <v>-0.01459034041261079</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0</v>
+        <v>0.08447325073842646</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4749265609972817</v>
+        <v>0.1219579486394138</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0</v>
+        <v>0.07473374076585439</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4749280309369548</v>
+        <v>0.1869293790555145</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0</v>
+        <v>0.05118045589140312</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4749292803856768</v>
+        <v>0.2145129668745406</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0</v>
+        <v>0.03310253500260738</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4749306400798741</v>
+        <v>0.229514003271977</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0</v>
+        <v>0.0104586068472272</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4749284351703648</v>
+        <v>0.217289089062595</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0</v>
+        <v>0.004668015734948236</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4749280309369548</v>
+        <v>0.2161590747516835</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0</v>
+        <v>0.001747320738414877</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4749271857216428</v>
+        <v>0.2149819505108271</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0</v>
+        <v>0.001061656172161539</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4749277369490201</v>
+        <v>0.2153569978617686</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0</v>
+        <v>0.0004711793451945394</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4749274062125937</v>
+        <v>0.2152369307220236</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0</v>
+        <v>0.0002064608088958555</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4749271122246592</v>
+        <v>0.2151807868083525</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>0</v>
+        <v>0.0001038869823003464</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4749271857216428</v>
+        <v>0.2151820352529914</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>0</v>
+        <v>4.101965893228747e-05</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4749267447397408</v>
+        <v>0.215157569099495</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>0</v>
+        <v>1.679858447626218e-05</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4749266344942653</v>
+        <v>0.215150113679368</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>0</v>
+        <v>4.724925521046201e-06</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4749265977457736</v>
+        <v>0.2151446960211461</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>0</v>
+        <v>1.275408036221018e-06</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4749267447397408</v>
+        <v>0.2151405694008842</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>0</v>
+        <v>-3.385354438485732e-06</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4749262670093472</v>
+        <v>0.2151341339216246</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>0</v>
+        <v>-2.431040204033588e-06</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4749272224701345</v>
+        <v>0.2151310414085677</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4749271857216428</v>
+        <v>0.215131004660076</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4749268549852164</v>
+        <v>0.2151306739236496</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4749272959671184</v>
+        <v>0.2151311149055515</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4749266712427572</v>
+        <v>0.2151304901811904</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4749264875002981</v>
+        <v>0.2151303064387313</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4749260832668881</v>
+        <v>0.2151299022053212</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432806</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.474925238051576</v>
+        <v>0.2151290569900093</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4749252013030844</v>
+        <v>0.2151290202415176</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.5384768609581863</v>
+        <v>0.534955561799899</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4749253482970516</v>
+        <v>0.2151291672354848</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.474925274800068</v>
+        <v>0.2151290937385012</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.138476860958186</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4749253482970516</v>
+        <v>0.2151291672354848</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.637571854792519</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4749253850455435</v>
+        <v>0.2151292039839768</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.474925274800068</v>
+        <v>0.2151290937385012</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.1909984303716907</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.47492571578197</v>
+        <v>0.2151295347204031</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.138476860958186</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4749256055364944</v>
+        <v>0.2151294244749276</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4749255687880025</v>
+        <v>0.2151293877264357</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4749254952910189</v>
+        <v>0.2151293142294521</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.637571854792519</v>
+        <v>-1.64290641471487</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4749254585425272</v>
+        <v>0.2151292774809604</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.637571854792519</v>
+        <v>-0.9169524225432806</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.474925238051576</v>
+        <v>0.2151290569900093</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.5384768609581863</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4749251645545924</v>
+        <v>0.2151289834930256</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.9169524225432805</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4749250910576088</v>
+        <v>0.215128909996042</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-2.037571854792519</v>
+        <v>-0.7169524225432805</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4749251278061007</v>
+        <v>0.2151289467445339</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.138476860958186</v>
+        <v>0.009001569628309336</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4749250175606252</v>
+        <v>0.2151288364990584</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4749251278061007</v>
+        <v>0.2151289467445339</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.082561524747701e-06</v>
+        <v>-4.22955549203955e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.138476860958186</v>
+        <v>0.7349555617998991</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4749254217940352</v>
+        <v>0.2151292407324684</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.0002957247197628021</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5539754264574855</v>
+        <v>-0.7200000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.00272795557975769</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.65</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.007305793464183807</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.004128895699977875</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.009001569628309336</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.003567416220903397</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001447807997465134</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9169524225432806</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.0002567209303379059</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0008797720074653625</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.000465095043182373</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0001737102866172791</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.009001569628309336</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.001820143312215805</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.000480014830827713</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001350350677967072</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.001120224595069885</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.001938860863447189</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.009001569628309336</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.001244500279426575</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.009001569628309336</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0001462511718273163</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1909984303716907</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0005766451358795166</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001182824373245239</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.001730509102344513</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001074690371751785</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.002293508499860764</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001829225569963455</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002941198647022247</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0009286589920520782</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.002175275236368179</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001740921288728714</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.534955561799899</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.00265323743224144</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.534955561799899</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.002807058393955231</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.534955561799899</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.003267258405685425</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.534955561799899</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.006109058856964111</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.001243717968463898</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001925379037857056</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001928534358739853</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0004571601748466492</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.002898778766393661</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0009971596300601959</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001756094396114349</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.003473866730928421</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002299264073371887</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.002469725906848907</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.003914110362529755</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.008821651339530945</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.534955561799899</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.006029713898897171</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1909984303716907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.564317593548912e-05</v>
+        <v>-0.0001132297395697096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1098756391847005</v>
+        <v>-0.1300792229893992</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.006052952259778976</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.003091484308242798</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.002944346517324448</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.0001297071576118469</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001158606261014938</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0004245378077030182</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0002787336707115173</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.001928526908159256</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.0002718642354011536</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.0009292289614677429</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0003980249166488647</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.000551760196685791</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.16</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.002172082662582397</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.006305858492851257</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.009001569628309336</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1099712823606361</v>
+        <v>-0.1302829440303154</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.3253861110976226</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.002626929432153702</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1909984303716907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>-0.110056073578537</v>
+        <v>0.5211140314134686</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-0.1138592459437131</v>
+        <v>0.02318369209896473</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.002401325851678848</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1909984303716907</v>
+        <v>0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>-0.2239153195222502</v>
+        <v>0.2415733494767121</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>0.04065629676820039</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.005703724920749664</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1909984303716907</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
-        <v>-0.2239892018635536</v>
+        <v>0.2996945139777425</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06765632548313105</v>
+        <v>0.04939259910281833</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.001767516136169434</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9169524225432805</v>
+        <v>0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>-0.0884635567722664</v>
+        <v>0.3578195469469761</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.006721339656880313</v>
+        <v>0.01307035425086451</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0009357035160064697</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9169524225432806</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>-0.1428246047627267</v>
+        <v>0.3345049254559909</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005054802979138153</v>
+        <v>0.007259810646202929</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01422202587127686</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1909984303716907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>-0.1394664796510547</v>
+        <v>0.3359432237700594</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0296347560280399</v>
+        <v>0.01525652312403987</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.009725805371999741</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.534955561799899</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>-0.0852288288384925</v>
+        <v>0.3592055528316989</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.01100510795767507</v>
+        <v>0.005991025513981075</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.006449393928050995</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>-0.09288798588976532</v>
+        <v>0.3559175474118902</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.008465071840913154</v>
+        <v>0.004264214459554022</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0003752186894416809</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>-0.08696730612569047</v>
+        <v>0.3584541785223549</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.003171480968060904</v>
+        <v>0.001676069304170846</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.005090810358524323</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.009001569628309336</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC69" t="n">
-        <v>-0.08909863252768305</v>
+        <v>0.3575370537525467</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001848062684090923</v>
+        <v>0.0009491347503788614</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.0008335411548614502</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.7169524225432804</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>-0.08857627168610552</v>
+        <v>0.3577582743768962</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0006562505770910311</v>
+        <v>0.000357880092280652</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.0009997449815273285</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>-0.08911269341112871</v>
+        <v>0.3575253122176472</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002995832812366127</v>
+        <v>0.0001656488687295067</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.002223514020442963</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>-0.08917129767969041</v>
+        <v>0.3574972965344696</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.401545328678301e-05</v>
+        <v>5.716404766525603e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001812975853681564</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>-0.08928263279871038</v>
+        <v>0.3574466405071262</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.477716780084401e-05</v>
+        <v>1.360244431470109e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.0002742484211921692</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>-0.08934756310967355</v>
+        <v>0.357415814024827</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>4.888583900422008e-06</v>
+        <v>4.062729281521043e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.0001982711255550385</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9169524225432806</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>-0.08935259661856526</v>
+        <v>0.357410799876628</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>8.983661582139364e-07</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.001496143639087677</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>-0.08935592432896665</v>
+        <v>0.3574065269590623</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.603006223559316e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001446124166250229</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7169524225432804</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>-0.08935670935394999</v>
+        <v>0.3574033593374975</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.800616699423805e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002137117087841034</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.44290641471487</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>-0.08936259684396244</v>
+        <v>0.3573979900105098</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>0</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.001496553421020508</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7169524225432805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>-0.0894373131227597</v>
+        <v>0.3573919972770794</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-0.06131849295370218</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>9.65707004070282e-05</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.009001569628309336</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>-0.1507560265674128</v>
+        <v>0.357386629488501</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>4.724040627479553e-05</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>-0.1508586901870591</v>
+        <v>0.3573866662369927</v>
       </c>
     </row>
     <row r="82">
@@ -66123,7 +66123,7 @@
         <v>0</v>
       </c>
       <c r="IY82" t="n">
-        <v>0.03884276342406302</v>
+        <v>0</v>
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.0006021596491336823</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>-0.07296047486886394</v>
+        <v>0.3573867764824682</v>
       </c>
     </row>
     <row r="83">
@@ -66918,7 +66918,7 @@
         <v>0</v>
       </c>
       <c r="IY83" t="n">
-        <v>0.03242030125742617</v>
+        <v>0</v>
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0002547241747379303</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>-0.04704932372256357</v>
+        <v>0.3573868499794519</v>
       </c>
     </row>
     <row r="84">
@@ -67713,7 +67713,7 @@
         <v>0</v>
       </c>
       <c r="IY84" t="n">
-        <v>0.0324589833099528</v>
+        <v>0</v>
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.007650043815374374</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>-0.01459034041261079</v>
+        <v>0.357387033721911</v>
       </c>
     </row>
     <row r="85">
@@ -68508,7 +68508,7 @@
         <v>0</v>
       </c>
       <c r="IY85" t="n">
-        <v>0.08447325073842646</v>
+        <v>0</v>
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.0147184357047081</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1219579486394138</v>
+        <v>0.3573885771585675</v>
       </c>
     </row>
     <row r="86">
@@ -69303,7 +69303,7 @@
         <v>0</v>
       </c>
       <c r="IY86" t="n">
-        <v>0.07473374076585439</v>
+        <v>0</v>
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.005693506449460983</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1869293790555145</v>
+        <v>0.3573900470982406</v>
       </c>
     </row>
     <row r="87">
@@ -70098,7 +70098,7 @@
         <v>0</v>
       </c>
       <c r="IY87" t="n">
-        <v>0.05118045589140312</v>
+        <v>0</v>
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.01928544789552689</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2145129668745406</v>
+        <v>0.3573912965469626</v>
       </c>
     </row>
     <row r="88">
@@ -70893,7 +70893,7 @@
         <v>0</v>
       </c>
       <c r="IY88" t="n">
-        <v>0.03310253500260738</v>
+        <v>0</v>
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.2180216908454895</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.229514003271977</v>
+        <v>0.3573926562411599</v>
       </c>
     </row>
     <row r="89">
@@ -71688,7 +71688,7 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0.0104586068472272</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01539726182818413</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.217289089062595</v>
+        <v>0.3573904513316506</v>
       </c>
     </row>
     <row r="90">
@@ -72483,7 +72483,7 @@
         <v>0</v>
       </c>
       <c r="IY90" t="n">
-        <v>0.004668015734948236</v>
+        <v>0</v>
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.04709767177700996</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.534955561799899</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2161590747516835</v>
+        <v>0.3573900470982406</v>
       </c>
     </row>
     <row r="91">
@@ -73278,7 +73278,7 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0.001747320738414877</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.03057241812348366</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.534955561799899</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2149819505108271</v>
+        <v>0.3573892018829286</v>
       </c>
     </row>
     <row r="92">
@@ -74073,7 +74073,7 @@
         <v>0</v>
       </c>
       <c r="IY92" t="n">
-        <v>0.001061656172161539</v>
+        <v>0</v>
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01181437820196152</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2153569978617686</v>
+        <v>0.3573897531103059</v>
       </c>
     </row>
     <row r="93">
@@ -74868,7 +74868,7 @@
         <v>0</v>
       </c>
       <c r="IY93" t="n">
-        <v>0.0004711793451945394</v>
+        <v>0</v>
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.007532402873039246</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.3</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2152369307220236</v>
+        <v>0.3573894223738795</v>
       </c>
     </row>
     <row r="94">
@@ -75663,7 +75663,7 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0.0002064608088958555</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01085547730326653</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2151807868083525</v>
+        <v>0.357389128385945</v>
       </c>
     </row>
     <row r="95">
@@ -76458,7 +76458,7 @@
         <v>0</v>
       </c>
       <c r="IY95" t="n">
-        <v>0.0001038869823003464</v>
+        <v>0</v>
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.004076763987541199</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2151820352529914</v>
+        <v>0.3573892018829286</v>
       </c>
     </row>
     <row r="96">
@@ -77253,7 +77253,7 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>4.101965893228747e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.003269024193286896</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.215157569099495</v>
+        <v>0.3573887609010267</v>
       </c>
     </row>
     <row r="97">
@@ -78048,7 +78048,7 @@
         <v>0</v>
       </c>
       <c r="IY97" t="n">
-        <v>1.679858447626218e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.002934705466032028</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.215150113679368</v>
+        <v>0.3573886506555511</v>
       </c>
     </row>
     <row r="98">
@@ -78843,7 +78843,7 @@
         <v>0</v>
       </c>
       <c r="IY98" t="n">
-        <v>4.724925521046201e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.004905633628368378</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2151446960211461</v>
+        <v>0.3573886139070594</v>
       </c>
     </row>
     <row r="99">
@@ -79638,7 +79638,7 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>1.275408036221018e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.001289829611778259</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2151405694008842</v>
+        <v>0.3573887609010267</v>
       </c>
     </row>
     <row r="100">
@@ -80433,7 +80433,7 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-3.385354438485732e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.02644321136176586</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2151341339216246</v>
+        <v>0.357388283170633</v>
       </c>
     </row>
     <row r="101">
@@ -81228,7 +81228,7 @@
         <v>0</v>
       </c>
       <c r="IY101" t="n">
-        <v>-2.431040204033588e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.03707119822502136</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.534955561799899</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2151310414085677</v>
+        <v>0.3573892386314203</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.002486389130353928</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.534955561799899</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.215131004660076</v>
+        <v>0.3573892018829286</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.007411904633045197</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2151306739236496</v>
+        <v>0.3573888711465022</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.004928354173898697</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2151311149055515</v>
+        <v>0.3573893121284041</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.001322679221630096</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2151304901811904</v>
+        <v>0.3573886874040431</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.001765292137861252</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2151303064387313</v>
+        <v>0.3573885036615839</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.001478008925914764</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2151299022053212</v>
+        <v>0.3573880994281738</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.0006190836429595947</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9169524225432806</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2151290569900093</v>
+        <v>0.3573872542128619</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.001793719828128815</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2151290202415176</v>
+        <v>0.3573872174643702</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.0002608746290206909</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.534955561799899</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2151291672354848</v>
+        <v>0.3573873644583374</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.0007655993103981018</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7349555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2151290937385012</v>
+        <v>0.3573872909613538</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.007377311587333679</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.009001569628309336</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2151291672354848</v>
+        <v>0.3573873644583374</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002587292343378067</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.009001569628309336</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2151292039839768</v>
+        <v>0.3573874012068293</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.005433849990367889</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2151290937385012</v>
+        <v>0.3573872909613538</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.001386560499668121</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1909984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2151295347204031</v>
+        <v>0.3573877319432557</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.0007360540330410004</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2151294244749276</v>
+        <v>0.3573876216977802</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.001135818660259247</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2151293877264357</v>
+        <v>0.3573875849492883</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.0005037859082221985</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2151293142294521</v>
+        <v>0.3573875114523047</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.001453619450330734</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.64290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2151292774809604</v>
+        <v>0.357387474703813</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.001627907156944275</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9169524225432806</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2151290569900093</v>
+        <v>0.3573872542128619</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.0003873184323310852</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2151289834930256</v>
+        <v>0.3573871807158783</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.0006082765758037567</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9169524225432805</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.215128909996042</v>
+        <v>0.3573871072188947</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.001133069396018982</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7169524225432805</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2151289467445339</v>
+        <v>0.3573871439673866</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.001412540674209595</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.009001569628309336</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2151288364990584</v>
+        <v>0.357387033721911</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.004648424685001373</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.02000000000000024</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2151289467445339</v>
+        <v>0.3573871439673866</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.22955549203955e-06</v>
+        <v>-4.082561524747701e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.001784637570381165</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7349555617998991</v>
+        <v>0.1600000000000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2151292407324684</v>
+        <v>0.357387437955321</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_3_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_3_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.0002957247197628021</v>
+        <v>-0.0002957768738269806</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.7200000000000001</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.00272795557975769</v>
+        <v>0.002727940678596497</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.65</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.007305793464183807</v>
+        <v>0.007305767387151718</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.5799999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.004128895699977875</v>
+        <v>0.004128873348236084</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.5799999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.003567416220903397</v>
+        <v>-0.003567412495613098</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.5799999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.001447807997465134</v>
+        <v>-0.001447811722755432</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.8599999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.0002567209303379059</v>
+        <v>0.0002567395567893982</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0008797720074653625</v>
+        <v>-0.0008797682821750641</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.000465095043182373</v>
+        <v>0.0004651062190532684</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0001737102866172791</v>
+        <v>-0.0001736953854560852</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.000480014830827713</v>
+        <v>0.0004799962043762207</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.001350350677967072</v>
+        <v>0.001350343227386475</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.001120224595069885</v>
+        <v>0.001120239496231079</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.2599999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.001938860863447189</v>
+        <v>0.001938894391059875</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.1199999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.001244500279426575</v>
+        <v>-0.001244515180587769</v>
       </c>
       <c r="JB17" t="n">
         <v>0.02000000000000007</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0001462511718273163</v>
+        <v>0.0001462437212467194</v>
       </c>
       <c r="JB18" t="n">
         <v>0.16</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0005766451358795166</v>
+        <v>0.000576656311750412</v>
       </c>
       <c r="JB19" t="n">
         <v>0.16</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.001182824373245239</v>
+        <v>0.001182816922664642</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.001074690371751785</v>
+        <v>0.001074682921171188</v>
       </c>
       <c r="JB22" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.002293508499860764</v>
+        <v>0.002293512225151062</v>
       </c>
       <c r="JB23" t="n">
         <v>0.5799999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.001829225569963455</v>
+        <v>0.001829199492931366</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.002941198647022247</v>
+        <v>0.002941206097602844</v>
       </c>
       <c r="JB25" t="n">
         <v>0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.0009286589920520782</v>
+        <v>0.0009286291897296906</v>
       </c>
       <c r="JB26" t="n">
         <v>0.5799999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.002175275236368179</v>
+        <v>0.002175293862819672</v>
       </c>
       <c r="JB27" t="n">
         <v>0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001740921288728714</v>
+        <v>0.001740910112857819</v>
       </c>
       <c r="JB28" t="n">
         <v>0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.00265323743224144</v>
+        <v>0.002653241157531738</v>
       </c>
       <c r="JB29" t="n">
         <v>0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.002807058393955231</v>
+        <v>0.002807054668664932</v>
       </c>
       <c r="JB30" t="n">
         <v>0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.003267258405685425</v>
+        <v>0.00326726958155632</v>
       </c>
       <c r="JB31" t="n">
         <v>0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.006109058856964111</v>
+        <v>0.006109051406383514</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.16</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.001243717968463898</v>
+        <v>-0.001243714243173599</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.1600000000000001</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.001925379037857056</v>
+        <v>0.001925382763147354</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.001928534358739853</v>
+        <v>0.001928538084030151</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.002898778766393661</v>
+        <v>0.002898786216974258</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.0009971596300601959</v>
+        <v>0.0009971670806407928</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.16</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.001756094396114349</v>
+        <v>0.001756079494953156</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.16</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.003473866730928421</v>
+        <v>0.003473855555057526</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.002469725906848907</v>
+        <v>0.002469711005687714</v>
       </c>
       <c r="JB42" t="n">
         <v>0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.003914110362529755</v>
+        <v>0.003914132714271545</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.006029713898897171</v>
+        <v>0.006029702723026276</v>
       </c>
       <c r="JB45" t="n">
         <v>0.5799999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.006052952259778976</v>
+        <v>-0.006052989512681961</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.003091484308242798</v>
+        <v>0.00309150293469429</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.5799999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.002944346517324448</v>
+        <v>-0.002944368869066238</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.0001297071576118469</v>
+        <v>0.0001296773552894592</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.8599999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.0004245378077030182</v>
+        <v>0.000424552708864212</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.8599999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.001928526908159256</v>
+        <v>0.001928500831127167</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.7199999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.0002718642354011536</v>
+        <v>0.0002718791365623474</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.0009292289614677429</v>
+        <v>0.0009292326867580414</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.1199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.0003980249166488647</v>
+        <v>0.0003980062901973724</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.1199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.000551760196685791</v>
+        <v>0.0005517452955245972</v>
       </c>
       <c r="JB57" t="n">
         <v>0.16</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.002172082662582397</v>
+        <v>0.002172090113162994</v>
       </c>
       <c r="JB58" t="n">
         <v>0.02000000000000007</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.006305858492851257</v>
+        <v>0.00630585104227066</v>
       </c>
       <c r="JB59" t="n">
         <v>0.1600000000000001</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.002626929432153702</v>
+        <v>-0.002626955509185791</v>
       </c>
       <c r="JB60" t="n">
         <v>0.4399999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.002401325851678848</v>
+        <v>0.002401329576969147</v>
       </c>
       <c r="JB61" t="n">
         <v>0.3</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.005703724920749664</v>
+        <v>0.005703721195459366</v>
       </c>
       <c r="JB62" t="n">
         <v>0.02000000000000007</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.001767516136169434</v>
+        <v>-0.001767504960298538</v>
       </c>
       <c r="JB63" t="n">
         <v>0.3</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.0009357035160064697</v>
+        <v>-0.000935681164264679</v>
       </c>
       <c r="JB64" t="n">
         <v>0.4399999999999999</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.01422202587127686</v>
+        <v>0.01422204449772835</v>
       </c>
       <c r="JB65" t="n">
         <v>0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.009725805371999741</v>
+        <v>0.009725801646709442</v>
       </c>
       <c r="JB66" t="n">
         <v>0.4399999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.006449393928050995</v>
+        <v>0.006449408829212189</v>
       </c>
       <c r="JB67" t="n">
         <v>0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.0003752186894416809</v>
+        <v>0.0003752149641513824</v>
       </c>
       <c r="JB68" t="n">
         <v>0.4399999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.005090810358524323</v>
+        <v>0.005090832710266113</v>
       </c>
       <c r="JB69" t="n">
         <v>0.1600000000000001</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.0008335411548614502</v>
+        <v>-0.0008335337042808533</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.7199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.0009997449815273285</v>
+        <v>-0.0009997375309467316</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.002223514020442963</v>
+        <v>-0.002223484218120575</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.001812975853681564</v>
+        <v>-0.001812964677810669</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.0002742484211921692</v>
+        <v>-0.0002742297947406769</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.8599999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.0001982711255550385</v>
+        <v>-0.0001982562243938446</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.001496143639087677</v>
+        <v>0.001496128737926483</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.8599999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.001446124166250229</v>
+        <v>-0.001446150243282318</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.8599999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002137117087841034</v>
+        <v>-0.002137109637260437</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.8599999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.001496553421020508</v>
+        <v>-0.001496549695730209</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>9.65707004070282e-05</v>
+        <v>9.657815098762512e-05</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.8599999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>4.724040627479553e-05</v>
+        <v>4.725158214569092e-05</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.8599999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.0006021596491336823</v>
+        <v>0.000602133572101593</v>
       </c>
       <c r="JB82" t="n">
         <v>0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.007650043815374374</v>
+        <v>0.00765005499124527</v>
       </c>
       <c r="JB84" t="n">
         <v>0.5799999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.0147184357047081</v>
+        <v>0.0147184282541275</v>
       </c>
       <c r="JB85" t="n">
         <v>0.7199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.005693506449460983</v>
+        <v>0.005693502724170685</v>
       </c>
       <c r="JB86" t="n">
         <v>0.9999999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.01928544789552689</v>
+        <v>0.01928542926907539</v>
       </c>
       <c r="JB87" t="n">
         <v>0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.2180216908454895</v>
+        <v>0.2180216014385223</v>
       </c>
       <c r="JB88" t="n">
         <v>0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.01539726182818413</v>
+        <v>0.01539728045463562</v>
       </c>
       <c r="JB89" t="n">
         <v>0.9999999999999998</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.04709767177700996</v>
+        <v>0.04709767550230026</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8599999999999999</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0.3573900470982406</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.03057241812348366</v>
+        <v>0.03057242371141911</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0.3573892018829286</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.01181437820196152</v>
+        <v>0.01181435585021973</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.02000000000000007</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0.3573897531103059</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.007532402873039246</v>
+        <v>0.007532428950071335</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0.3573894223738795</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.01085547730326653</v>
+        <v>0.01085547357797623</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
         <v>0.357389128385945</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.004076763987541199</v>
+        <v>0.004076778888702393</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
         <v>0.3573892018829286</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.003269024193286896</v>
+        <v>0.003269053995609283</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
         <v>0.3573887609010267</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.002934705466032028</v>
+        <v>0.002934668213129044</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.001289829611778259</v>
+        <v>0.001289837062358856</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.4399999999999999</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.02644321136176586</v>
+        <v>0.02644322067499161</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4399999999999999</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
         <v>0.357388283170633</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.03707119822502136</v>
+        <v>0.03707121685147285</v>
       </c>
       <c r="JB101" t="n">
         <v>0.1600000000000001</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.002486389130353928</v>
+        <v>0.002486377954483032</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.007411904633045197</v>
+        <v>0.0074118971824646</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.004928354173898697</v>
+        <v>0.004928361624479294</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.001322679221630096</v>
+        <v>0.001322664320468903</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.001765292137861252</v>
+        <v>0.00176529586315155</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.001478008925914764</v>
+        <v>-0.001478012651205063</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.0006190836429595947</v>
+        <v>-0.0006190687417984009</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.0002608746290206909</v>
+        <v>0.0002608597278594971</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.0007655993103981018</v>
+        <v>0.0007655806839466095</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.007377311587333679</v>
+        <v>0.007377289235591888</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002587292343378067</v>
+        <v>-0.00258728489279747</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.005433849990367889</v>
+        <v>0.005433846265077591</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.001386560499668121</v>
+        <v>-0.001386575400829315</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.0007360540330410004</v>
+        <v>0.0007360726594924927</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.001135818660259247</v>
+        <v>-0.001135829836130142</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.0005037859082221985</v>
+        <v>-0.0005037747323513031</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.001453619450330734</v>
+        <v>-0.001453634351491928</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.001627907156944275</v>
+        <v>-0.00162789598107338</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.0003873184323310852</v>
+        <v>0.0003873296082019806</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.0006082765758037567</v>
+        <v>-0.000608295202255249</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.001133069396018982</v>
+        <v>-0.001133061945438385</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.1199999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.001412540674209595</v>
+        <v>0.00141255185008049</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.1199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.004648424685001373</v>
+        <v>0.004648461937904358</v>
       </c>
       <c r="JB125" t="n">
         <v>0.02000000000000024</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.001784637570381165</v>
+        <v>0.001784656196832657</v>
       </c>
       <c r="JB126" t="n">
         <v>0.1600000000000003</v>
